--- a/fhir/StructureDefinition-ehealth-observation.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -374,7 +374,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -678,7 +678,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -761,7 +761,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -844,7 +844,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -867,7 +867,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1069,7 +1069,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1128,7 +1128,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1161,7 +1161,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1173,7 +1173,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1287,7 +1287,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1367,7 +1367,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1404,7 +1404,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1426,7 +1426,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1516,7 +1516,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -1854,7 +1854,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-observation.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-observation.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-observation.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1299,6 +1299,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -6907,7 +6911,7 @@
         <v>410</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>411</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -6916,10 +6920,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -6930,10 +6934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6959,10 +6963,10 @@
         <v>407</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7013,7 +7017,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7025,7 +7029,7 @@
         <v>410</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>411</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -7034,10 +7038,10 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7048,10 +7052,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7077,16 +7081,16 @@
         <v>233</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7115,7 +7119,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -7133,7 +7137,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7151,10 +7155,10 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>340</v>
@@ -7168,10 +7172,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7197,16 +7201,16 @@
         <v>233</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7234,10 +7238,10 @@
         <v>354</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7255,7 +7259,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7273,10 +7277,10 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>340</v>
@@ -7290,10 +7294,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7316,17 +7320,17 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7375,7 +7379,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7399,7 +7403,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7410,10 +7414,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7439,10 +7443,10 @@
         <v>153</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7493,7 +7497,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7514,10 +7518,10 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7528,10 +7532,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7554,16 +7558,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7613,7 +7617,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7634,10 +7638,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7648,10 +7652,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7674,16 +7678,16 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7733,7 +7737,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7754,10 +7758,10 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -7768,10 +7772,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7797,16 +7801,16 @@
         <v>389</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7855,7 +7859,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7876,10 +7880,10 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7890,10 +7894,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8008,10 +8012,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8128,10 +8132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8250,10 +8254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8279,13 +8283,13 @@
         <v>233</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>247</v>
@@ -8335,7 +8339,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>91</v>
@@ -8353,7 +8357,7 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>251</v>
@@ -8370,10 +8374,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8399,13 +8403,13 @@
         <v>311</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>313</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>315</v>
@@ -8457,7 +8461,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8475,7 +8479,7 @@
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>318</v>
@@ -8492,10 +8496,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8521,13 +8525,13 @@
         <v>233</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>325</v>
@@ -8558,10 +8562,10 @@
         <v>335</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8579,7 +8583,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8614,10 +8618,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8701,7 +8705,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8736,10 +8740,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8765,10 +8769,10 @@
         <v>81</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>392</v>
@@ -8823,7 +8827,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>

--- a/fhir/StructureDefinition-ehealth-observation.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-observation.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-observation.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
